--- a/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
+++ b/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
@@ -63,6 +63,111 @@
     <t xml:space="preserve">SortOrder</t>
   </si>
   <si>
+    <t xml:space="preserve">P-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Martinez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website Redesign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance Update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frank Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-31</t>
+  </si>
+  <si>
     <t xml:space="preserve">P-009</t>
   </si>
   <si>
@@ -81,9 +186,6 @@
     <t xml:space="preserve">2025-02-15</t>
   </si>
   <si>
-    <t xml:space="preserve">2025-05-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">P-003</t>
   </si>
   <si>
@@ -93,15 +195,15 @@
     <t xml:space="preserve">Carol Davis</t>
   </si>
   <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-02-01</t>
   </si>
   <si>
     <t xml:space="preserve">2025-04-30</t>
   </si>
   <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
     <t xml:space="preserve">P-007</t>
   </si>
   <si>
@@ -111,48 +213,12 @@
     <t xml:space="preserve">Grace Lee</t>
   </si>
   <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
     <t xml:space="preserve">2024-12-01</t>
   </si>
   <si>
     <t xml:space="preserve">2025-06-15</t>
   </si>
   <si>
-    <t xml:space="preserve">P-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance Update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eva Martinez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-15</t>
-  </si>
-  <si>
     <t xml:space="preserve">P-002</t>
   </si>
   <si>
@@ -166,72 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">2025-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website Redesign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytics Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frank Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henry Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-31</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -336,12 +336,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -437,10 +441,10 @@
         <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>20000</v>
+        <v>25000</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
@@ -456,19 +460,19 @@
       </c>
       <c r="J2" s="1" t="n">
         <f aca="false">D2-E2</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K2" s="1" t="n">
         <f aca="false">ROUND(E2/D2*100,1)</f>
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1" t="str">
         <f aca="false">IF(K2&gt;=90,"Critical",IF(K2&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>Warning</v>
       </c>
       <c r="M2" s="1" t="n">
         <f aca="false">IF(L2="Critical",1,IF(L2="Warning",2,3))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -482,10 +486,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>30000</v>
+        <v>50000</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>30000</v>
+        <v>35000</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -501,19 +505,19 @@
       </c>
       <c r="J3" s="1" t="n">
         <f aca="false">D3-E3</f>
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="K3" s="1" t="n">
         <f aca="false">ROUND(E3/D3*100,1)</f>
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="L3" s="1" t="str">
         <f aca="false">IF(K3&gt;=90,"Critical",IF(K3&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>Warning</v>
       </c>
       <c r="M3" s="1" t="n">
         <f aca="false">IF(L3="Critical",1,IF(L3="Warning",2,3))</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -527,75 +531,75 @@
         <v>28</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>60000</v>
+        <v>15000</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>55000</v>
+        <v>8000</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>32</v>
       </c>
       <c r="J4" s="1" t="n">
         <f aca="false">D4-E4</f>
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">ROUND(E4/D4*100,1)</f>
-        <v>91.7</v>
+        <v>53.3</v>
       </c>
       <c r="L4" s="1" t="str">
         <f aca="false">IF(K4&gt;=90,"Critical",IF(K4&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M4" s="1" t="n">
         <f aca="false">IF(L4="Critical",1,IF(L4="Warning",2,3))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="D5" s="1" t="n">
-        <v>15000</v>
+        <v>45000</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>8000</v>
+        <v>20000</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>36</v>
       </c>
       <c r="J5" s="1" t="n">
         <f aca="false">D5-E5</f>
-        <v>7000</v>
+        <v>25000</v>
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">ROUND(E5/D5*100,1)</f>
-        <v>53.3</v>
+        <v>44.4</v>
       </c>
       <c r="L5" s="1" t="str">
         <f aca="false">IF(K5&gt;=90,"Critical",IF(K5&gt;=70,"Warning","On Track"))</f>
@@ -617,61 +621,61 @@
         <v>39</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>25000</v>
+        <v>120000</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>18000</v>
+        <v>45000</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>41</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>42</v>
       </c>
       <c r="J6" s="1" t="n">
         <f aca="false">D6-E6</f>
-        <v>7000</v>
+        <v>75000</v>
       </c>
       <c r="K6" s="1" t="n">
         <f aca="false">ROUND(E6/D6*100,1)</f>
-        <v>72</v>
+        <v>37.5</v>
       </c>
       <c r="L6" s="1" t="str">
         <f aca="false">IF(K6&gt;=90,"Critical",IF(K6&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>On Track</v>
       </c>
       <c r="M6" s="1" t="n">
         <f aca="false">IF(L6="Critical",1,IF(L6="Warning",2,3))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D7" s="1" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="G7" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>40</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>46</v>
@@ -681,19 +685,19 @@
       </c>
       <c r="J7" s="1" t="n">
         <f aca="false">D7-E7</f>
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="K7" s="1" t="n">
         <f aca="false">ROUND(E7/D7*100,1)</f>
-        <v>90</v>
+        <v>28.6</v>
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">IF(K7&gt;=90,"Critical",IF(K7&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M7" s="1" t="n">
         <f aca="false">IF(L7="Critical",1,IF(L7="Warning",2,3))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -707,61 +711,61 @@
         <v>50</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>50000</v>
+        <v>20000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>35000</v>
+        <v>20000</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>52</v>
       </c>
       <c r="J8" s="1" t="n">
         <f aca="false">D8-E8</f>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1" t="n">
         <f aca="false">ROUND(E8/D8*100,1)</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">IF(K8&gt;=90,"Critical",IF(K8&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>Critical</v>
       </c>
       <c r="M8" s="1" t="n">
         <f aca="false">IF(L8="Critical",1,IF(L8="Warning",2,3))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>35000</v>
+        <v>30000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>10000</v>
+        <v>30000</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>57</v>
@@ -771,19 +775,19 @@
       </c>
       <c r="J9" s="1" t="n">
         <f aca="false">D9-E9</f>
-        <v>25000</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1" t="n">
         <f aca="false">ROUND(E9/D9*100,1)</f>
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="L9" s="1" t="str">
         <f aca="false">IF(K9&gt;=90,"Critical",IF(K9&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Critical</v>
       </c>
       <c r="M9" s="1" t="n">
         <f aca="false">IF(L9="Critical",1,IF(L9="Warning",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>59</v>
@@ -800,16 +804,16 @@
         <v>62</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45000</v>
+        <v>60000</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>20000</v>
+        <v>55000</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>63</v>
@@ -819,19 +823,19 @@
       </c>
       <c r="J10" s="1" t="n">
         <f aca="false">D10-E10</f>
-        <v>25000</v>
+        <v>5000</v>
       </c>
       <c r="K10" s="1" t="n">
         <f aca="false">ROUND(E10/D10*100,1)</f>
-        <v>44.4</v>
+        <v>91.7</v>
       </c>
       <c r="L10" s="1" t="str">
         <f aca="false">IF(K10&gt;=90,"Critical",IF(K10&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Critical</v>
       </c>
       <c r="M10" s="1" t="n">
         <f aca="false">IF(L10="Critical",1,IF(L10="Warning",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -845,16 +849,16 @@
         <v>67</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>120000</v>
+        <v>80000</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>45000</v>
+        <v>72000</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>68</v>
@@ -864,19 +868,19 @@
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">D11-E11</f>
-        <v>75000</v>
+        <v>8000</v>
       </c>
       <c r="K11" s="1" t="n">
         <f aca="false">ROUND(E11/D11*100,1)</f>
-        <v>37.5</v>
+        <v>90</v>
       </c>
       <c r="L11" s="1" t="str">
         <f aca="false">IF(K11&gt;=90,"Critical",IF(K11&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Critical</v>
       </c>
       <c r="M11" s="1" t="n">
         <f aca="false">IF(L11="Critical",1,IF(L11="Warning",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -917,7 +921,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>4</v>
@@ -979,23 +983,23 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
@@ -1009,7 +1013,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
@@ -1023,7 +1027,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -1037,7 +1041,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -1051,7 +1055,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
@@ -1065,7 +1069,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -1079,7 +1083,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>28</v>
+        <v>62</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
@@ -1093,7 +1097,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>67</v>
+        <v>39</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
@@ -1107,7 +1111,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -1121,7 +1125,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>

--- a/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
+++ b/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
@@ -63,6 +63,87 @@
     <t xml:space="preserve">SortOrder</t>
   </si>
   <si>
+    <t xml:space="preserve">P-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iris Chen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carol Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile App v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">P-005</t>
   </si>
   <si>
@@ -72,12 +153,6 @@
     <t xml:space="preserve">Eva Martinez</t>
   </si>
   <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-04-01</t>
   </si>
   <si>
@@ -93,9 +168,6 @@
     <t xml:space="preserve">Alice Johnson</t>
   </si>
   <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-01-15</t>
   </si>
   <si>
@@ -111,12 +183,6 @@
     <t xml:space="preserve">Jack Anderson</t>
   </si>
   <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-01</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-09-30</t>
   </si>
   <si>
@@ -166,72 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">2025-10-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iris Chen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carol Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grace Lee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile App v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-15</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -389,44 +389,44 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -441,10 +441,10 @@
         <v>15</v>
       </c>
       <c r="D2" s="1" t="n">
-        <v>25000</v>
+        <v>20000</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>18000</v>
+        <v>20000</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>16</v>
@@ -460,19 +460,19 @@
       </c>
       <c r="J2" s="1" t="n">
         <f aca="false">D2-E2</f>
-        <v>7000</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1" t="n">
         <f aca="false">ROUND(E2/D2*100,1)</f>
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="L2" s="1" t="str">
         <f aca="false">IF(K2&gt;=90,"Critical",IF(K2&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>Critical</v>
       </c>
       <c r="M2" s="1" t="n">
         <f aca="false">IF(L2="Critical",1,IF(L2="Warning",2,3))</f>
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -486,10 +486,10 @@
         <v>22</v>
       </c>
       <c r="D3" s="1" t="n">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>35000</v>
+        <v>30000</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>16</v>
@@ -505,244 +505,247 @@
       </c>
       <c r="J3" s="1" t="n">
         <f aca="false">D3-E3</f>
-        <v>15000</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1" t="n">
         <f aca="false">ROUND(E3/D3*100,1)</f>
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="L3" s="1" t="str">
         <f aca="false">IF(K3&gt;=90,"Critical",IF(K3&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>Critical</v>
       </c>
       <c r="M3" s="1" t="n">
         <f aca="false">IF(L3="Critical",1,IF(L3="Warning",2,3))</f>
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>15000</v>
+        <v>60000</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>8000</v>
+        <v>55000</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J4" s="1" t="n">
         <f aca="false">D4-E4</f>
-        <v>7000</v>
+        <v>5000</v>
       </c>
       <c r="K4" s="1" t="n">
         <f aca="false">ROUND(E4/D4*100,1)</f>
-        <v>53.3</v>
+        <v>91.7</v>
       </c>
       <c r="L4" s="1" t="str">
         <f aca="false">IF(K4&gt;=90,"Critical",IF(K4&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Critical</v>
       </c>
       <c r="M4" s="1" t="n">
         <f aca="false">IF(L4="Critical",1,IF(L4="Warning",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>45000</v>
+        <v>80000</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>20000</v>
+        <v>72000</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J5" s="1" t="n">
         <f aca="false">D5-E5</f>
-        <v>25000</v>
+        <v>8000</v>
       </c>
       <c r="K5" s="1" t="n">
         <f aca="false">ROUND(E5/D5*100,1)</f>
-        <v>44.4</v>
+        <v>90</v>
       </c>
       <c r="L5" s="1" t="str">
         <f aca="false">IF(K5&gt;=90,"Critical",IF(K5&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Critical</v>
       </c>
       <c r="M5" s="1" t="n">
         <f aca="false">IF(L5="Critical",1,IF(L5="Warning",2,3))</f>
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="H6" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="J6" s="1" t="n">
         <f aca="false">D6-E6</f>
-        <v>75000</v>
+        <v>7000</v>
       </c>
       <c r="K6" s="1" t="n">
         <f aca="false">ROUND(E6/D6*100,1)</f>
-        <v>37.5</v>
+        <v>72</v>
       </c>
       <c r="L6" s="1" t="str">
         <f aca="false">IF(K6&gt;=90,"Critical",IF(K6&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Warning</v>
       </c>
       <c r="M6" s="1" t="n">
         <f aca="false">IF(L6="Critical",1,IF(L6="Warning",2,3))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E7" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>10000</v>
-      </c>
       <c r="F7" s="1" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J7" s="1" t="n">
         <f aca="false">D7-E7</f>
-        <v>25000</v>
+        <v>15000</v>
       </c>
       <c r="K7" s="1" t="n">
         <f aca="false">ROUND(E7/D7*100,1)</f>
-        <v>28.6</v>
+        <v>70</v>
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">IF(K7&gt;=90,"Critical",IF(K7&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Warning</v>
       </c>
       <c r="M7" s="1" t="n">
         <f aca="false">IF(L7="Critical",1,IF(L7="Warning",2,3))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="n">
-        <v>20000</v>
+        <v>15000</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>20000</v>
+        <v>8000</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="H8" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I8" s="1" t="s">
         <v>53</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>30</v>
       </c>
       <c r="J8" s="1" t="n">
         <f aca="false">D8-E8</f>
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K8" s="1" t="n">
         <f aca="false">ROUND(E8/D8*100,1)</f>
-        <v>100</v>
+        <v>53.3</v>
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">IF(K8&gt;=90,"Critical",IF(K8&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M8" s="1" t="n">
         <f aca="false">IF(L8="Critical",1,IF(L8="Warning",2,3))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -756,16 +759,16 @@
         <v>56</v>
       </c>
       <c r="D9" s="1" t="n">
-        <v>30000</v>
+        <v>45000</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>30000</v>
+        <v>20000</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>57</v>
@@ -775,90 +778,87 @@
       </c>
       <c r="J9" s="1" t="n">
         <f aca="false">D9-E9</f>
-        <v>0</v>
+        <v>25000</v>
       </c>
       <c r="K9" s="1" t="n">
         <f aca="false">ROUND(E9/D9*100,1)</f>
-        <v>100</v>
+        <v>44.4</v>
       </c>
       <c r="L9" s="1" t="str">
         <f aca="false">IF(K9&gt;=90,"Critical",IF(K9&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M9" s="1" t="n">
         <f aca="false">IF(L9="Critical",1,IF(L9="Warning",2,3))</f>
-        <v>1</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="D10" s="1" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>60000</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>55000</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>64</v>
       </c>
       <c r="J10" s="1" t="n">
         <f aca="false">D10-E10</f>
-        <v>5000</v>
+        <v>75000</v>
       </c>
       <c r="K10" s="1" t="n">
         <f aca="false">ROUND(E10/D10*100,1)</f>
-        <v>91.7</v>
+        <v>37.5</v>
       </c>
       <c r="L10" s="1" t="str">
         <f aca="false">IF(K10&gt;=90,"Critical",IF(K10&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M10" s="1" t="n">
         <f aca="false">IF(L10="Critical",1,IF(L10="Warning",2,3))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="1" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="D11" s="1" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>68</v>
@@ -868,19 +868,19 @@
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">D11-E11</f>
-        <v>8000</v>
+        <v>25000</v>
       </c>
       <c r="K11" s="1" t="n">
         <f aca="false">ROUND(E11/D11*100,1)</f>
-        <v>90</v>
+        <v>28.6</v>
       </c>
       <c r="L11" s="1" t="str">
         <f aca="false">IF(K11&gt;=90,"Critical",IF(K11&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
+        <v>On Track</v>
       </c>
       <c r="M11" s="1" t="n">
         <f aca="false">IF(L11="Critical",1,IF(L11="Warning",2,3))</f>
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -921,7 +921,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>4</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
@@ -1013,7 +1013,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
@@ -1027,7 +1027,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -1041,7 +1041,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
@@ -1069,7 +1069,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>29</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>39</v>
+        <v>61</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
@@ -1111,7 +1111,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -1125,7 +1125,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>

--- a/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
+++ b/assets/libreoffice_calc_njc/3281db55-73e1-4889-bff4-829581706ec6/ProjTimeline_L3_09.xlsx
@@ -22,7 +22,88 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="78">
+  <si>
+    <t xml:space="preserve">P-003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carol Davis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Completed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Training Portal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iris Chen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API Gateway</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grace Lee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In Progress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">High</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobile App v2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bob Smith</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critical</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2024-11-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-15</t>
+  </si>
   <si>
     <t xml:space="preserve">Project ID</t>
   </si>
@@ -51,187 +132,109 @@
     <t xml:space="preserve">End Date</t>
   </si>
   <si>
-    <t xml:space="preserve">Remaining Budget</t>
+    <t xml:space="preserve">Remaining Bud”% SpentBudget Statusget</t>
   </si>
   <si>
     <t xml:space="preserve">% Spent</t>
   </si>
   <si>
+    <t xml:space="preserve">SortOrder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-010</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compliance Update</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jack Anderson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRM Integration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">David Wilson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Migration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Henry Taylor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analytics Dashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frank Brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planning</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Audit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eva Martinez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remaining Bud% SpentgBudget Statuset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Website Redesign</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alice Johnson</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-30</t>
+  </si>
+  <si>
     <t xml:space="preserve">Budget Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SortOrder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Training Portal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iris Chen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carol Davis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medium</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-02-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API Gateway</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grace Lee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">In Progress</t>
-  </si>
-  <si>
-    <t xml:space="preserve">High</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-12-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mobile App v2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bob Smith</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Critical</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2024-11-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-05-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Audit</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eva Martinez</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-04-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-07-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Website Redesign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Alice Johnson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-010</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Compliance Update</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jack Anderson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CRM Integration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">David Wilson</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-03-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Migration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Henry Taylor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-01-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-12-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P-006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Analytics Dashboard</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Frank Brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-06-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2025-10-31</t>
   </si>
   <si>
     <t xml:space="preserve">Count</t>
@@ -259,8 +262,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -336,7 +340,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -345,7 +349,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -386,59 +398,68 @@
   <dimension ref="A1:N11"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="10" min="1" style="1" width="8.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="11" min="11" style="2" width="8.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="12" style="1" width="8.53"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="E1" s="1" t="n">
+        <v>30000</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="1" t="e">
+        <f aca="false">D1-#REF!:l10e2k2=E1/D1*100=IF(K1&gt;=90,"Critical",IF(K1&gt;=70,"Warning","on track))))</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="K1" s="2" t="n">
+        <f aca="false">ROUND(E1/D1*100,1)</f>
+        <v>100</v>
+      </c>
+      <c r="L1" s="1" t="str">
+        <f aca="false">IF(K1&gt;=90,"Critical",IF(K1&gt;=70,"Warning","On Track"))</f>
+        <v>Critical</v>
+      </c>
+      <c r="M1" s="1" t="n">
+        <f aca="false">IF(L1="Critical",1,IF(L1="Warning",2,3))</f>
+        <v>1</v>
+      </c>
+      <c r="N1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="n">
         <v>20000</v>
@@ -447,22 +468,22 @@
         <v>20000</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="J2" s="1" t="n">
         <f aca="false">D2-E2</f>
         <v>0</v>
       </c>
-      <c r="K2" s="1" t="n">
+      <c r="K2" s="2" t="n">
         <f aca="false">ROUND(E2/D2*100,1)</f>
         <v>100</v>
       </c>
@@ -477,39 +498,39 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>60000</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>55000</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="1" t="s">
         <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>30000</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>30000</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="J3" s="1" t="n">
         <f aca="false">D3-E3</f>
-        <v>0</v>
-      </c>
-      <c r="K3" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="K3" s="2" t="n">
         <f aca="false">ROUND(E3/D3*100,1)</f>
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="L3" s="1" t="str">
         <f aca="false">IF(K3&gt;=90,"Critical",IF(K3&gt;=70,"Warning","On Track"))</f>
@@ -519,45 +540,42 @@
         <f aca="false">IF(L3="Critical",1,IF(L3="Warning",2,3))</f>
         <v>1</v>
       </c>
-      <c r="N3" s="1" t="s">
-        <v>26</v>
-      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="D4" s="1" t="n">
-        <v>60000</v>
+        <v>80000</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>55000</v>
+        <v>72000</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="J4" s="1" t="n">
         <f aca="false">D4-E4</f>
-        <v>5000</v>
-      </c>
-      <c r="K4" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="K4" s="2" t="n">
         <f aca="false">ROUND(E4/D4*100,1)</f>
-        <v>91.7</v>
+        <v>90</v>
       </c>
       <c r="L4" s="1" t="str">
         <f aca="false">IF(K4&gt;=90,"Critical",IF(K4&gt;=70,"Warning","On Track"))</f>
@@ -570,174 +588,171 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="J5" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="1" t="n">
-        <v>80000</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>72000</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G5" s="1" t="s">
+      <c r="K5" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="L5" s="1" t="str">
+        <f aca="false">IF(K6&gt;=90,"Critical",IF(K6&gt;=70,"Warning","On Track"))</f>
+        <v>On Track</v>
+      </c>
+      <c r="M5" s="1" t="s">
         <v>38</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="J5" s="1" t="n">
-        <f aca="false">D5-E5</f>
-        <v>8000</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <f aca="false">ROUND(E5/D5*100,1)</f>
-        <v>90</v>
-      </c>
-      <c r="L5" s="1" t="str">
-        <f aca="false">IF(K5&gt;=90,"Critical",IF(K5&gt;=70,"Warning","On Track"))</f>
-        <v>Critical</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <f aca="false">IF(L5="Critical",1,IF(L5="Warning",2,3))</f>
-        <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="C6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="D6" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>8000</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="I6" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>25000</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>18000</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="J6" s="1" t="n">
         <f aca="false">D6-E6</f>
         <v>7000</v>
       </c>
-      <c r="K6" s="1" t="n">
+      <c r="K6" s="2" t="n">
         <f aca="false">ROUND(E6/D6*100,1)</f>
-        <v>72</v>
+        <v>53.3</v>
       </c>
       <c r="L6" s="1" t="str">
         <f aca="false">IF(K6&gt;=90,"Critical",IF(K6&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>On Track</v>
       </c>
       <c r="M6" s="1" t="n">
         <f aca="false">IF(L6="Critical",1,IF(L6="Warning",2,3))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="D7" s="1" t="n">
+        <v>45000</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>20000</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>47</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>35000</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>49</v>
       </c>
       <c r="J7" s="1" t="n">
         <f aca="false">D7-E7</f>
-        <v>15000</v>
-      </c>
-      <c r="K7" s="1" t="n">
+        <v>25000</v>
+      </c>
+      <c r="K7" s="2" t="n">
         <f aca="false">ROUND(E7/D7*100,1)</f>
-        <v>70</v>
+        <v>44.4</v>
       </c>
       <c r="L7" s="1" t="str">
         <f aca="false">IF(K7&gt;=90,"Critical",IF(K7&gt;=70,"Warning","On Track"))</f>
-        <v>Warning</v>
+        <v>On Track</v>
       </c>
       <c r="M7" s="1" t="n">
         <f aca="false">IF(L7="Critical",1,IF(L7="Warning",2,3))</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="D8" s="1" t="n">
+        <v>120000</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>45000</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>15000</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>8000</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>53</v>
       </c>
       <c r="J8" s="1" t="n">
         <f aca="false">D8-E8</f>
-        <v>7000</v>
-      </c>
-      <c r="K8" s="1" t="n">
+        <v>75000</v>
+      </c>
+      <c r="K8" s="2" t="n">
         <f aca="false">ROUND(E8/D8*100,1)</f>
-        <v>53.3</v>
+        <v>37.5</v>
       </c>
       <c r="L8" s="1" t="str">
         <f aca="false">IF(K8&gt;=90,"Critical",IF(K8&gt;=70,"Warning","On Track"))</f>
@@ -750,25 +765,25 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="n">
+        <v>35000</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>45000</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>30</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>57</v>
@@ -780,9 +795,9 @@
         <f aca="false">D9-E9</f>
         <v>25000</v>
       </c>
-      <c r="K9" s="1" t="n">
+      <c r="K9" s="2" t="n">
         <f aca="false">ROUND(E9/D9*100,1)</f>
-        <v>44.4</v>
+        <v>28.6</v>
       </c>
       <c r="L9" s="1" t="str">
         <f aca="false">IF(K9&gt;=90,"Critical",IF(K9&gt;=70,"Warning","On Track"))</f>
@@ -794,71 +809,71 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D10" s="1" t="n">
-        <v>120000</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="H10" s="1" t="s">
+      <c r="D10" s="3" t="n">
+        <v>25000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>18000</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="1" t="n">
-        <f aca="false">D10-E10</f>
-        <v>75000</v>
-      </c>
-      <c r="K10" s="1" t="n">
-        <f aca="false">ROUND(E10/D10*100,1)</f>
-        <v>37.5</v>
-      </c>
-      <c r="L10" s="1" t="str">
+      <c r="J10" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <f aca="false">E10/D10*100</f>
+        <v>72</v>
+      </c>
+      <c r="L10" s="3" t="str">
         <f aca="false">IF(K10&gt;=90,"Critical",IF(K10&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
-      </c>
-      <c r="M10" s="1" t="n">
+        <v>Warning</v>
+      </c>
+      <c r="M10" s="3" t="n">
         <f aca="false">IF(L10="Critical",1,IF(L10="Warning",2,3))</f>
-        <v>3</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="N10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D11" s="1" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E11" s="1" t="n">
         <v>35000</v>
       </c>
-      <c r="E11" s="1" t="n">
-        <v>10000</v>
-      </c>
       <c r="F11" s="1" t="s">
-        <v>67</v>
+        <v>17</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>68</v>
@@ -868,19 +883,19 @@
       </c>
       <c r="J11" s="1" t="n">
         <f aca="false">D11-E11</f>
-        <v>25000</v>
-      </c>
-      <c r="K11" s="1" t="n">
+        <v>15000</v>
+      </c>
+      <c r="K11" s="2" t="n">
         <f aca="false">ROUND(E11/D11*100,1)</f>
-        <v>28.6</v>
+        <v>70</v>
       </c>
       <c r="L11" s="1" t="str">
         <f aca="false">IF(K11&gt;=90,"Critical",IF(K11&gt;=70,"Warning","On Track"))</f>
-        <v>On Track</v>
+        <v>Warning</v>
       </c>
       <c r="M11" s="1" t="n">
         <f aca="false">IF(L11="Critical",1,IF(L11="Warning",2,3))</f>
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -906,58 +921,58 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="C1" s="3" t="s">
         <v>72</v>
       </c>
+      <c r="D1" s="3" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B2" s="1" t="n">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="3" t="n">
         <v>190000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="3" t="n">
         <v>95.4</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B3" s="1" t="n">
+      <c r="A3" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="3" t="n">
         <v>75000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="3" t="n">
         <v>71</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B4" s="1" t="n">
+      <c r="A4" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="3" t="n">
         <v>215000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="3" t="n">
         <v>41</v>
       </c>
     </row>
@@ -983,23 +998,23 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="1" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="D1" s="2" t="s">
+    <row r="1" s="3" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>76</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="B2" s="1" t="n">
         <v>1</v>
@@ -1013,7 +1028,7 @@
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="B3" s="1" t="n">
         <v>1</v>
@@ -1027,7 +1042,7 @@
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B4" s="1" t="n">
         <v>1</v>
@@ -1041,7 +1056,7 @@
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B5" s="1" t="n">
         <v>1</v>
@@ -1055,7 +1070,7 @@
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="B6" s="1" t="n">
         <v>1</v>
@@ -1069,7 +1084,7 @@
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B7" s="1" t="n">
         <v>1</v>
@@ -1083,7 +1098,7 @@
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="n">
         <v>1</v>
@@ -1097,7 +1112,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B9" s="1" t="n">
         <v>1</v>
@@ -1111,7 +1126,7 @@
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="n">
         <v>1</v>
@@ -1125,7 +1140,7 @@
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B11" s="1" t="n">
         <v>1</v>
